--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12 11:24:52</t>
+          <t>2026-08-12 16:02:51</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-12 16:02:51</t>
+          <t>2026-08-13 11:28:14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-13 11:28:14</t>
+          <t>2026-08-13 16:03:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-13 16:03:54</t>
+          <t>2026-08-14 11:25:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-14 11:25:25</t>
+          <t>2026-08-14 16:00:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-14 16:00:51</t>
+          <t>2026-08-15 10:14:46</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14:46</t>
+          <t>2026-08-15 15:15:06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-15 15:15:06</t>
+          <t>2026-08-16 10:22:31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-16 10:22:31</t>
+          <t>2026-08-16 15:17:09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-16 15:17:09</t>
+          <t>2026-08-17 10:20:53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:53</t>
+          <t>2026-08-17 15:37:43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-17 15:37:43</t>
+          <t>2026-08-18 10:17:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,12 +1915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C25">
@@ -1941,12 +1941,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C26">
@@ -1967,12 +1967,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C27">
@@ -1993,12 +1993,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C28">
@@ -2019,12 +2019,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C29">
@@ -2045,12 +2045,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C30">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,12 +2097,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C32">
@@ -2123,12 +2123,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C33">
@@ -2149,12 +2149,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C34">
@@ -2175,12 +2175,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C35">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12 16:02:51</t>
+          <t>2026-08-13 11:28:14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13 11:28:14</t>
+          <t>2026-08-13 16:03:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-13 16:03:54</t>
+          <t>2026-08-14 11:25:25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-14 11:25:25</t>
+          <t>2026-08-14 16:00:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-14 16:00:51</t>
+          <t>2026-08-15 10:14:46</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14:46</t>
+          <t>2026-08-15 15:15:06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-15 15:15:06</t>
+          <t>2026-08-16 10:22:31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-16 10:22:31</t>
+          <t>2026-08-16 15:17:09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-16 15:17:09</t>
+          <t>2026-08-17 10:20:53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:53</t>
+          <t>2026-08-17 15:37:43</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-17 15:37:43</t>
+          <t>2026-08-18 10:17:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,12 +1915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C25">
@@ -1941,12 +1941,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C26">
@@ -1967,12 +1967,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C27">
@@ -1993,12 +1993,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C28">
@@ -2019,12 +2019,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C29">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,12 +2071,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C31">
@@ -2097,12 +2097,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C32">
@@ -2123,12 +2123,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C33">
@@ -2149,12 +2149,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C34">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>63.67</t>
+          <t>69.38</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价63.67低于硬止损78.00</t>
+          <t>现价69.38低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>60.40</t>
+          <t>66.90</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>40.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价63.67低于硬止损78.00</t>
+          <t>现价69.38低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-13 11:28:14</t>
+          <t>2026-08-13 16:03:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13 16:03:54</t>
+          <t>2026-08-14 11:25:25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14 11:25:25</t>
+          <t>2026-08-14 16:00:51</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-14 16:00:51</t>
+          <t>2026-08-15 10:14:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14:46</t>
+          <t>2026-08-15 15:15:06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-15 15:15:06</t>
+          <t>2026-08-16 10:22:31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-16 10:22:31</t>
+          <t>2026-08-16 15:17:09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-16 15:17:09</t>
+          <t>2026-08-17 10:20:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:53</t>
+          <t>2026-08-17 15:37:43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-17 15:37:43</t>
+          <t>2026-08-18 10:17:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,12 +1915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C25">
@@ -1941,12 +1941,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C26">
@@ -1967,12 +1967,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C27">
@@ -1993,12 +1993,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C28">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,12 +2045,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C30">
@@ -2071,12 +2071,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C31">
@@ -2097,12 +2097,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C32">
@@ -2123,12 +2123,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C33">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>69.38</t>
+          <t>69.06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价69.38低于硬止损78.00</t>
+          <t>现价69.06低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>34.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>66.90</t>
+          <t>65.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.10</t>
+          <t>39.81</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价69.38低于硬止损78.00</t>
+          <t>现价69.06低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-13 16:03:54</t>
+          <t>2026-08-14 11:25:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-14 11:25:25</t>
+          <t>2026-08-14 16:00:51</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14 16:00:51</t>
+          <t>2026-08-15 10:14:46</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14:46</t>
+          <t>2026-08-15 15:15:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-15 15:15:06</t>
+          <t>2026-08-16 10:22:31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-16 10:22:31</t>
+          <t>2026-08-16 15:17:09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-16 15:17:09</t>
+          <t>2026-08-17 10:20:53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:53</t>
+          <t>2026-08-17 15:37:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-17 15:37:43</t>
+          <t>2026-08-18 10:17:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,12 +1915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C25">
@@ -1941,12 +1941,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C26">
@@ -1967,12 +1967,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C27">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C29">
@@ -2045,12 +2045,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C30">
@@ -2071,12 +2071,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C31">
@@ -2097,12 +2097,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C32">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>69.06</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价69.06低于硬止损78.00</t>
+          <t>现价69.67低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.19</t>
+          <t>34.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>65.72</t>
+          <t>64.13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.81</t>
+          <t>40.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价69.06低于硬止损78.00</t>
+          <t>现价69.67低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-14 11:25:25</t>
+          <t>2026-08-14 16:00:51</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-14 16:00:51</t>
+          <t>2026-08-15 10:14:46</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14:46</t>
+          <t>2026-08-15 15:15:06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-15 15:15:06</t>
+          <t>2026-08-16 10:22:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-16 10:22:31</t>
+          <t>2026-08-16 15:17:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-16 15:17:09</t>
+          <t>2026-08-17 10:20:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:53</t>
+          <t>2026-08-17 15:37:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-17 15:37:43</t>
+          <t>2026-08-18 10:17:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,12 +1915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C25">
@@ -1941,12 +1941,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C26">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,12 +1993,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C28">
@@ -2019,12 +2019,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C29">
@@ -2045,12 +2045,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C30">
@@ -2071,12 +2071,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C31">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>69.67</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价69.67低于硬止损78.00</t>
+          <t>现价69.82低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.00</t>
+          <t>33.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>63.50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.10</t>
+          <t>39.89</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价69.67低于硬止损78.00</t>
+          <t>现价69.82低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-14 16:00:51</t>
+          <t>2026-08-15 10:14:46</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14:46</t>
+          <t>2026-08-15 15:15:06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-15 15:15:06</t>
+          <t>2026-08-16 10:22:31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-16 10:22:31</t>
+          <t>2026-08-16 15:17:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-16 15:17:09</t>
+          <t>2026-08-17 10:20:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:53</t>
+          <t>2026-08-17 15:37:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:37:43</t>
+          <t>2026-08-18 10:17:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,12 +1915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C25">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,12 +1967,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C27">
@@ -1993,12 +1993,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C28">
@@ -2019,12 +2019,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C29">
@@ -2045,12 +2045,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C30">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>69.82</t>
+          <t>71.06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价69.82低于硬止损78.00</t>
+          <t>现价71.06低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.79</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>63.50</t>
+          <t>61.47</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价69.82低于硬止损78.00</t>
+          <t>现价71.06低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-15 10:14:46</t>
+          <t>2026-08-15 15:15:06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-15 15:15:06</t>
+          <t>2026-08-16 10:22:31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-16 10:22:31</t>
+          <t>2026-08-16 15:17:09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-16 15:17:09</t>
+          <t>2026-08-17 10:20:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:53</t>
+          <t>2026-08-17 15:37:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-17 15:37:43</t>
+          <t>2026-08-18 10:17:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C26">
@@ -1967,12 +1967,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C27">
@@ -1993,12 +1993,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C28">
@@ -2019,12 +2019,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C29">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71.06</t>
+          <t>71.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价71.06低于硬止损78.00</t>
+          <t>现价71.90低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>33.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>61.47</t>
+          <t>61.88</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价71.06低于硬止损78.00</t>
+          <t>现价71.90低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-15 15:15:06</t>
+          <t>2026-08-16 10:22:31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-16 10:22:31</t>
+          <t>2026-08-16 15:17:09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-16 15:17:09</t>
+          <t>2026-08-17 10:20:53</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:53</t>
+          <t>2026-08-17 15:37:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-17 15:37:43</t>
+          <t>2026-08-18 10:17:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,12 +1915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C25">
@@ -1941,12 +1941,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C26">
@@ -1967,12 +1967,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C27">
@@ -1993,12 +1993,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C28">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71.90</t>
+          <t>75.59</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价71.90低于硬止损78.00</t>
+          <t>现价75.59低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.67</t>
+          <t>33.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>61.88</t>
+          <t>62.37</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价71.90低于硬止损78.00</t>
+          <t>现价75.59低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-16 10:22:31</t>
+          <t>2026-08-16 15:17:09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-16 15:17:09</t>
+          <t>2026-08-17 10:20:53</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:53</t>
+          <t>2026-08-17 15:37:43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-17 15:37:43</t>
+          <t>2026-08-18 10:17:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,12 +1915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C25">
@@ -1941,12 +1941,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C26">
@@ -1967,12 +1967,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C27">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>75.59</t>
+          <t>74.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价75.59低于硬止损78.00</t>
+          <t>现价74.95低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>62.37</t>
+          <t>61.50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.32</t>
+          <t>38.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价75.59低于硬止损78.00</t>
+          <t>现价74.95低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-16 15:17:09</t>
+          <t>2026-08-17 10:20:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:53</t>
+          <t>2026-08-17 15:37:43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-17 15:37:43</t>
+          <t>2026-08-18 10:17:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,12 +1915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C25">
@@ -1941,12 +1941,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C26">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74.95</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价74.95低于硬止损78.00</t>
+          <t>现价70.59低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>61.50</t>
+          <t>57.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>36.94</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价74.95低于硬止损78.00</t>
+          <t>现价70.59低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:20:53</t>
+          <t>2026-08-17 15:37:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-17 15:37:43</t>
+          <t>2026-08-18 10:17:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,12 +1915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C25">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价70.59低于硬止损78.00</t>
+          <t>现价70.89低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.63</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>58.05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>36.94</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价70.59低于硬止损78.00</t>
+          <t>现价70.89低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-17 15:37:43</t>
+          <t>2026-08-18 10:17:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:17:04</t>
+          <t>2026-08-18 15:23:13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:23:13</t>
+          <t>2026-08-19 10:19:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:19:57</t>
+          <t>2026-08-19 15:23:59</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19 15:23:59</t>
+          <t>2026-08-20 10:18:26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价70.89低于硬止损78.00</t>
+          <t>现价71.05低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>33.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>58.05</t>
+          <t>58.28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价70.89低于硬止损78.00</t>
+          <t>现价71.05低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:18:26</t>
+          <t>2026-08-20 15:25:49</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,7 +326,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71.05</t>
+          <t>71.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价71.05低于硬止损78.00</t>
+          <t>现价71.00低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.07</t>
+          <t>32.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>58.28</t>
+          <t>59.48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>37.64</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价71.05低于硬止损78.00</t>
+          <t>现价71.00低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20 15:25:49</t>
+          <t>2026-08-21 10:24:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71.00</t>
+          <t>70.11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价71.00低于硬止损78.00</t>
+          <t>现价70.11低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32.96</t>
+          <t>34.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>59.48</t>
+          <t>62.59</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价71.00低于硬止损78.00</t>
+          <t>现价70.11低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21 10:24:43</t>
+          <t>2026-08-21 15:27:09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>70.11</t>
+          <t>70.51</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价70.11低于硬止损78.00</t>
+          <t>现价70.51低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.01</t>
+          <t>34.10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>62.59</t>
+          <t>62.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价70.11低于硬止损78.00</t>
+          <t>现价70.51低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21 15:27:09</t>
+          <t>2026-08-22 10:17:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>70.51</t>
+          <t>75.51</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价70.51低于硬止损78.00</t>
+          <t>现价75.51低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.10</t>
+          <t>35.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>64.88</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>39.96</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价70.51低于硬止损78.00</t>
+          <t>现价75.51低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-22 10:17:12</t>
+          <t>2026-08-22 15:17:41</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>75.51</t>
+          <t>77.66</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价75.51低于硬止损78.00</t>
+          <t>现价77.66低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.48</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>64.88</t>
+          <t>64.84</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.96</t>
+          <t>39.90</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价75.51低于硬止损78.00</t>
+          <t>现价77.66低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-22 15:17:41</t>
+          <t>2026-08-23 10:24:35</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>77.66</t>
+          <t>77.04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价77.66低于硬止损78.00</t>
+          <t>现价77.04低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>35.75</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>64.84</t>
+          <t>65.05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.90</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价77.66低于硬止损78.00</t>
+          <t>现价77.04低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23 10:24:35</t>
+          <t>2026-08-23 15:19:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>77.04</t>
+          <t>76.65</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价77.04低于硬止损78.00</t>
+          <t>现价76.65低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>35.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>65.05</t>
+          <t>65.36</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>38.80</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价77.04低于硬止损78.00</t>
+          <t>现价76.65低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23 15:19:30</t>
+          <t>2026-08-24 10:23:52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,12 +1577,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C12">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -161,7 +161,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>76.65</t>
+          <t>79.31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>回避</t>
+          <t>观察</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价76.65低于硬止损78.00</t>
+          <t>核心事件尚未由公告/互动易/财报确认</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.60</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>65.36</t>
+          <t>68.48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.80</t>
+          <t>42.68</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>回避</t>
+          <t>观察</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价76.65低于硬止损78.00</t>
+          <t>核心事件尚未由公告/互动易/财报确认</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24 10:23:52</t>
+          <t>2026-08-24 15:43:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,12 +1551,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C11">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>79.31</t>
+          <t>78.49</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>36.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>68.48</t>
+          <t>68.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24 15:43:12</t>
+          <t>2026-08-25 10:19:24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,12 +1525,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C10">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2580,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-25 10:19:24</t>
+          <t>2026-08-25 15:28:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,12 +1499,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C9">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-25 15:28:43</t>
+          <t>2026-08-26 10:26:03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,12 +1473,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C8">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2528,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-26 10:26:03</t>
+          <t>2026-08-26 15:30:03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,12 +1447,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C7">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-26 15:30:03</t>
+          <t>2026-08-27 19:02:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,12 +1421,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C6">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2476,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>78.49</t>
+          <t>84.40</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>35.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>68.00</t>
+          <t>66.34</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42.68</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-27 19:02:57</t>
+          <t>2026-08-28 01:53:35</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,12 +1395,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C5">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>84.40</t>
+          <t>85.40</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.79</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>66.34</t>
+          <t>65.94</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>6.97</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-28 01:53:35</t>
+          <t>2026-08-28 20:36:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,12 +1369,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C4">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>85.40</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>65.94</t>
+          <t>65.43</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>6.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-28 20:36:25</t>
+          <t>2026-08-29 02:59:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,12 +1343,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>82.62</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>65.43</t>
+          <t>65.18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1317,12 +1317,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-29 02:59:57</t>
+          <t>2026-08-29 15:44:45</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C2">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>82.62</t>
+          <t>85.34</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>65.18</t>
+          <t>67.10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.95</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-29 15:44:45</t>
+          <t>2026-08-29 20:49:51</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>85.34</t>
+          <t>84.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>67.10</t>
+          <t>66.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-29 20:49:51</t>
+          <t>2026-08-30 14:22:18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>84.54</t>
+          <t>80.17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>66.80</t>
+          <t>65.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-30 14:22:18</t>
+          <t>2026-08-30 20:12:52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2294,7 +2294,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>80.17</t>
+          <t>78.54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>65.80</t>
+          <t>64.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>43.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-30 20:12:52</t>
+          <t>2026-08-31 14:49:59</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31 14:49:59</t>
+          <t>2026-08-31 22:24:07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31 22:24:07</t>
+          <t>2026-09-01 14:08:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01 14:08:54</t>
+          <t>2026-09-01 19:59:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01 19:59:54</t>
+          <t>2026-09-02 13:34:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-02 13:34:22</t>
+          <t>2026-09-02 19:42:51</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-02 19:42:51</t>
+          <t>2026-09-03 13:35:02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2112,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -161,7 +161,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>78.54</t>
+          <t>75.43</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>观察</t>
+          <t>回避</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>核心事件尚未由公告/互动易/财报确认</t>
+          <t>现价75.43低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>64.69</t>
+          <t>61.30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>观察</t>
+          <t>回避</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>核心事件尚未由公告/互动易/财报确认</t>
+          <t>现价75.43低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-03 13:35:02</t>
+          <t>2026-09-03 19:42:36</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>75.43</t>
+          <t>76.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价75.43低于硬止损78.00</t>
+          <t>现价76.00低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>33.94</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>61.30</t>
+          <t>60.43</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.86</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价75.43低于硬止损78.00</t>
+          <t>现价76.00低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-03 19:42:36</t>
+          <t>2026-09-04 13:40:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2580,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>76.00</t>
+          <t>74.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价76.00低于硬止损78.00</t>
+          <t>现价74.83低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.94</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>60.43</t>
+          <t>60.44</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价76.00低于硬止损78.00</t>
+          <t>现价74.83低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:22</t>
+          <t>2026-09-04 19:43:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74.83</t>
+          <t>74.67</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价74.83低于硬止损78.00</t>
+          <t>现价74.67低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>33.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>60.44</t>
+          <t>59.94</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价74.83低于硬止损78.00</t>
+          <t>现价74.67低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04 19:43:30</t>
+          <t>2026-09-05 13:27:07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2528,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>71.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价74.67低于硬止损78.00</t>
+          <t>现价71.92低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.40</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>58.48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>38.69</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价74.67低于硬止损78.00</t>
+          <t>现价71.92低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-05 13:27:07</t>
+          <t>2026-09-05 18:54:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71.92</t>
+          <t>71.60</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价71.92低于硬止损78.00</t>
+          <t>现价71.60低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>32.42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>58.48</t>
+          <t>57.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.69</t>
+          <t>38.60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价71.92低于硬止损78.00</t>
+          <t>现价71.60低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-05 18:54:47</t>
+          <t>2026-09-06 13:41:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2476,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-06 13:41:54</t>
+          <t>2026-09-06 19:20:08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-06 19:20:08</t>
+          <t>2026-09-07 13:52:05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1904,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:52:05</t>
+          <t>2026-09-07 21:00:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1878,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:00:22</t>
+          <t>2026-09-08 13:45:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45:00</t>
+          <t>2026-09-08 19:44:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08 19:44:04</t>
+          <t>2026-09-09 13:49:28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:28</t>
+          <t>2026-09-09 19:49:50</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2294,7 +2294,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:49:50</t>
+          <t>2026-09-10 13:43:55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10 13:43:55</t>
+          <t>2026-09-10 19:48:17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10 19:48:17</t>
+          <t>2026-09-11 13:43:35</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11 13:43:35</t>
+          <t>2026-09-11 19:47:49</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:47:49</t>
+          <t>2026-09-12 13:30:33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:30:33</t>
+          <t>2026-09-12 19:14:36</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-12 19:14:36</t>
+          <t>2026-09-13 13:48:41</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2112,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71.60</t>
+          <t>66.20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价71.60低于硬止损78.00</t>
+          <t>现价66.20低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>31.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>57.93</t>
+          <t>54.50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.60</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价71.60低于硬止损78.00</t>
+          <t>现价66.20低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13 13:48:41</t>
+          <t>2026-09-13 20:16:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>66.20</t>
+          <t>66.40</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价66.20低于硬止损78.00</t>
+          <t>现价66.40低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31.12</t>
+          <t>31.24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.50</t>
+          <t>54.45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价66.20低于硬止损78.00</t>
+          <t>现价66.40低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:16:25</t>
+          <t>2026-09-14 13:57:28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>66.40</t>
+          <t>63.20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价66.40低于硬止损78.00</t>
+          <t>现价63.20低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31.24</t>
+          <t>30.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.45</t>
+          <t>53.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>37.81</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价66.40低于硬止损78.00</t>
+          <t>现价63.20低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:57:28</t>
+          <t>2026-09-14 21:20:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>63.20</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价63.20低于硬止损78.00</t>
+          <t>现价63.47低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.37</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>53.73</t>
+          <t>53.76</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价63.20低于硬止损78.00</t>
+          <t>现价63.47低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14 21:20:25</t>
+          <t>2026-09-15 13:58:37</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15 13:58:37</t>
+          <t>2026-09-15 20:06:06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15 20:06:06</t>
+          <t>2026-09-16 13:48:51</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16 13:48:51</t>
+          <t>2026-09-16 20:01:26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16 20:01:26</t>
+          <t>2026-09-17 13:54:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1904,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>60.55</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价63.47低于硬止损78.00</t>
+          <t>现价60.55低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.40</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>53.76</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价63.47低于硬止损78.00</t>
+          <t>现价60.55低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17 13:54:53</t>
+          <t>2026-09-17 20:04:21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1878,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -115,7 +115,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60.55</t>
+          <t>60.52</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价60.55低于硬止损78.00</t>
+          <t>现价60.52低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>54.40</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价60.55低于硬止损78.00</t>
+          <t>现价60.52低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17 20:04:21</t>
+          <t>2026-09-18 13:41:38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,12 +2591,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C51">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -115,7 +115,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60.52</t>
+          <t>61.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价60.52低于硬止损78.00</t>
+          <t>现价61.78低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.40</t>
+          <t>53.38</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.20</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价60.52低于硬止损78.00</t>
+          <t>现价61.78低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18 13:41:38</t>
+          <t>2026-09-18 19:48:07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,12 +2565,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C50">
@@ -2591,12 +2591,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C51">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18 19:48:07</t>
+          <t>2026-09-19 13:35:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,12 +2539,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C49">
@@ -2565,12 +2565,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C50">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>61.78</t>
+          <t>61.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价61.78低于硬止损78.00</t>
+          <t>现价61.00低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>50.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价61.78低于硬止损78.00</t>
+          <t>现价61.00低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19 13:35:56</t>
+          <t>2026-09-19 19:30:59</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C48">
@@ -2539,12 +2539,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C49">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>61.00</t>
+          <t>60.20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价61.00低于硬止损78.00</t>
+          <t>现价60.20低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50.66</t>
+          <t>51.01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价61.00低于硬止损78.00</t>
+          <t>现价60.20低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19 19:30:59</t>
+          <t>2026-09-20 13:55:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1748,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,12 +2487,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C47">
@@ -2513,12 +2513,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C48">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60.20</t>
+          <t>59.13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价60.20低于硬止损78.00</t>
+          <t>现价59.13低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>28.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>51.01</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价60.20低于硬止损78.00</t>
+          <t>现价59.13低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20 13:55:01</t>
+          <t>2026-09-20 19:47:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1722,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,12 +2461,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C46">
@@ -2487,12 +2487,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C47">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59.13</t>
+          <t>59.07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价59.13低于硬止损78.00</t>
+          <t>现价59.07低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>50.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37.00</t>
+          <t>36.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价59.13低于硬止损78.00</t>
+          <t>现价59.07低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20 19:47:40</t>
+          <t>2026-09-21 14:01:20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1696,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,12 +2435,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C45">
@@ -2461,12 +2461,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C46">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59.07</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价59.07低于硬止损78.00</t>
+          <t>现价58.82低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>51.14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价59.07低于硬止损78.00</t>
+          <t>现价58.82低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21 14:01:20</t>
+          <t>2026-09-21 21:20:11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,12 +2409,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C44">
@@ -2435,12 +2435,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C45">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>57.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价58.82低于硬止损78.00</t>
+          <t>现价57.99低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>51.14</t>
+          <t>50.07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价58.82低于硬止损78.00</t>
+          <t>现价57.99低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21 21:20:11</t>
+          <t>2026-09-22 13:57:19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,12 +2383,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C43">
@@ -2409,12 +2409,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C44">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:57:19</t>
+          <t>2026-09-22 20:02:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,12 +2357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C42">
@@ -2383,12 +2383,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C43">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22 20:02:12</t>
+          <t>2026-09-23 13:41:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,12 +2331,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C41">
@@ -2357,12 +2357,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C42">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23 13:41:48</t>
+          <t>2026-09-23 20:07:38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,12 +2305,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C40">
@@ -2331,12 +2331,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C41">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23 20:07:38</t>
+          <t>2026-09-24 13:57:24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C39">
@@ -2305,12 +2305,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C40">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>57.99</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价57.99低于硬止损78.00</t>
+          <t>现价56.00低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50.07</t>
+          <t>46.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>6.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价57.99低于硬止损78.00</t>
+          <t>现价56.00低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24 13:57:24</t>
+          <t>2026-09-24 20:11:20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,12 +2253,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C38">
@@ -2279,12 +2279,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C39">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>56.00</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价56.00低于硬止损78.00</t>
+          <t>现价56.26低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>27.76</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.70</t>
+          <t>47.27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>34.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价56.00低于硬止损78.00</t>
+          <t>现价56.26低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24 20:11:20</t>
+          <t>2026-09-25 13:59:18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C37">
@@ -2253,12 +2253,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C38">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价56.26低于硬止损78.00</t>
+          <t>现价57.97低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.27</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>35.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价56.26低于硬止损78.00</t>
+          <t>现价57.97低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25 13:59:18</t>
+          <t>2026-09-25 20:12:12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,12 +2201,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C36">
@@ -2227,12 +2227,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C37">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价57.97低于硬止损78.00</t>
+          <t>现价58.84低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35.03</t>
+          <t>35.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价57.97低于硬止损78.00</t>
+          <t>现价58.84低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25 20:12:12</t>
+          <t>2026-09-26 13:58:52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C35">
@@ -2201,12 +2201,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C36">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>57.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价58.84低于硬止损78.00</t>
+          <t>现价57.77低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.88</t>
+          <t>47.58</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35.02</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价58.84低于硬止损78.00</t>
+          <t>现价57.77低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-26 13:58:52</t>
+          <t>2026-09-26 19:45:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,12 +2149,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C34">
@@ -2175,12 +2175,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C35">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>57.77</t>
+          <t>57.51</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价57.77低于硬止损78.00</t>
+          <t>现价57.51低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.58</t>
+          <t>47.60</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>35.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价57.77低于硬止损78.00</t>
+          <t>现价57.51低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-26 19:45:53</t>
+          <t>2026-09-27 14:25:57</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,12 +2123,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C33">
@@ -2149,12 +2149,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C34">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>57.51</t>
+          <t>55.03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价57.51低于硬止损78.00</t>
+          <t>现价55.03低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>27.80</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.60</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价57.51低于硬止损78.00</t>
+          <t>现价55.03低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27 14:25:57</t>
+          <t>2026-09-27 20:26:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,12 +2097,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C32">
@@ -2123,12 +2123,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C33">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>55.31</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价55.03低于硬止损78.00</t>
+          <t>现价55.31低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.80</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价55.03低于硬止损78.00</t>
+          <t>现价55.31低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27 20:26:00</t>
+          <t>2026-09-28 14:31:09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,12 +2071,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C31">
@@ -2097,12 +2097,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C32">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55.31</t>
+          <t>55.08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价55.31低于硬止损78.00</t>
+          <t>现价55.08低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>43.87</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.40</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>32.91</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价55.31低于硬止损78.00</t>
+          <t>现价55.08低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:31:09</t>
+          <t>2026-09-28 22:27:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,12 +2045,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C30">
@@ -2071,12 +2071,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C31">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55.08</t>
+          <t>57.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价55.08低于硬止损78.00</t>
+          <t>现价57.80低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>34.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价55.08低于硬止损78.00</t>
+          <t>现价57.80低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28 22:27:30</t>
+          <t>2026-09-29 14:41:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C29">
@@ -2045,12 +2045,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C30">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29 14:41:47</t>
+          <t>2026-09-29 21:18:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,12 +1993,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C28">
@@ -2019,12 +2019,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C29">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29 21:18:47</t>
+          <t>2026-09-30 14:28:20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,12 +1967,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C27">
@@ -1993,12 +1993,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C28">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-30 14:28:20</t>
+          <t>2026-09-30 20:59:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C26">
@@ -1967,12 +1967,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C27">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-30 20:59:40</t>
+          <t>2026-10-01 15:02:43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,12 +1915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C25">
@@ -1941,12 +1941,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C26">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>57.80</t>
+          <t>56.53</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价57.80低于硬止损78.00</t>
+          <t>现价56.53低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>42.91</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>32.99</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价57.80低于硬止损78.00</t>
+          <t>现价56.53低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01 15:02:43</t>
+          <t>2026-10-01 21:53:16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,12 +1915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C25">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>56.53</t>
+          <t>55.70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价56.53低于硬止损78.00</t>
+          <t>现价55.70低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>27.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.91</t>
+          <t>42.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32.99</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价56.53低于硬止损78.00</t>
+          <t>现价55.70低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01 21:53:16</t>
+          <t>2026-10-02 14:50:27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,12 +1889,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C24">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55.70</t>
+          <t>55.16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价55.70低于硬止损78.00</t>
+          <t>现价55.16低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.30</t>
+          <t>27.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.69</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>32.55</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价55.70低于硬止损78.00</t>
+          <t>现价55.16低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02 14:50:27</t>
+          <t>2026-10-02 21:09:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,12 +1863,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C23">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55.16</t>
+          <t>53.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价55.16低于硬止损78.00</t>
+          <t>现价53.88低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价55.16低于硬止损78.00</t>
+          <t>现价53.88低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02 21:09:30</t>
+          <t>2026-10-03 14:14:36</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,12 +1837,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C22">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>53.88</t>
+          <t>55.50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价53.88低于硬止损78.00</t>
+          <t>现价55.50低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>27.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>41.90</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>33.82</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价53.88低于硬止损78.00</t>
+          <t>现价55.50低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-03 14:14:36</t>
+          <t>2026-10-03 20:00:58</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,12 +1811,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C21">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55.50</t>
+          <t>55.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价55.50低于硬止损78.00</t>
+          <t>现价55.84低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,7 +413,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.21</t>
+          <t>27.20</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.90</t>
+          <t>41.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>33.90</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价55.50低于硬止损78.00</t>
+          <t>现价55.84低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-03 20:00:58</t>
+          <t>2026-10-04 14:41:34</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,12 +1785,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C20">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-28 21:31:01</t>
+          <t>2026-10-29 14:51:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28 21:31:01</t>
+          <t>2026-10-29 14:51:22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55.84</t>
+          <t>53.01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价55.84低于硬止损78.00</t>
+          <t>现价53.01低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28 21:31:01</t>
+          <t>2026-10-29 14:51:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.20</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28 21:31:01</t>
+          <t>2026-10-29 14:51:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.80</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28 21:31:01</t>
+          <t>2026-10-29 14:51:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28 21:31:01</t>
+          <t>2026-10-29 14:51:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33.90</t>
+          <t>32.91</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价55.84低于硬止损78.00</t>
+          <t>现价53.01低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-04 14:41:34</t>
+          <t>2026-10-04 20:50:45</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,12 +1759,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C19">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-28 21:31:01</t>
+          <t>2026-10-29 14:51:22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 14:51:22</t>
+          <t>2026-10-29 21:42:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29 14:51:22</t>
+          <t>2026-10-29 21:42:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>53.01</t>
+          <t>52.50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价53.01低于硬止损78.00</t>
+          <t>现价52.50低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29 14:51:22</t>
+          <t>2026-10-29 21:42:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>25.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29 14:51:22</t>
+          <t>2026-10-29 21:42:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>39.21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29 14:51:22</t>
+          <t>2026-10-29 21:42:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29 14:51:22</t>
+          <t>2026-10-29 21:42:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>32.73</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价53.01低于硬止损78.00</t>
+          <t>现价52.50低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-04 20:50:45</t>
+          <t>2026-10-05 14:42:04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,12 +1733,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C18">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-28 21:31:01</t>
+          <t>2026-10-29 14:51:22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-29 14:51:22</t>
+          <t>2026-10-29 21:42:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 21:42:30</t>
+          <t>2026-10-30 14:54:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29 21:42:30</t>
+          <t>2026-10-30 14:54:51</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.50</t>
+          <t>50.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价52.50低于硬止损78.00</t>
+          <t>现价50.96低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29 21:42:30</t>
+          <t>2026-10-30 14:54:51</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>24.84</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29 21:42:30</t>
+          <t>2026-10-30 14:54:51</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>36.03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29 21:42:30</t>
+          <t>2026-10-30 14:54:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29 21:42:30</t>
+          <t>2026-10-30 14:54:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32.73</t>
+          <t>32.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价52.50低于硬止损78.00</t>
+          <t>现价50.96低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05 14:42:04</t>
+          <t>2026-10-05 23:15:32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,12 +1707,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C17">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-28 21:31:01</t>
+          <t>2026-10-29 14:51:22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-29 14:51:22</t>
+          <t>2026-10-29 21:42:30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-29 21:42:30</t>
+          <t>2026-10-30 14:54:51</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 14:54:51</t>
+          <t>2026-10-30 21:32:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-30 14:54:51</t>
+          <t>2026-10-30 21:32:24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -326,12 +326,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50.96</t>
+          <t>50.30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -386,7 +386,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>现价50.96低于硬止损78.00</t>
+          <t>现价50.30低于硬止损78.00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-30 14:54:51</t>
+          <t>2026-10-30 21:32:24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -413,12 +413,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>24.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-30 14:54:51</t>
+          <t>2026-10-30 21:32:24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>36.03</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-30 14:54:51</t>
+          <t>2026-10-30 21:32:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-30 14:54:51</t>
+          <t>2026-10-30 21:32:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>31.80</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>现价50.96低于硬止损78.00</t>
+          <t>现价50.30低于硬止损78.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05 23:15:32</t>
+          <t>2026-10-06 15:22:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,7 +1629,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,12 +1681,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C16">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-28 21:31:01</t>
+          <t>2026-10-29 14:51:22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-29 14:51:22</t>
+          <t>2026-10-29 21:42:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-29 21:42:30</t>
+          <t>2026-10-30 14:54:51</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-30 14:54:51</t>
+          <t>2026-10-30 21:32:24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 21:32:24</t>
+          <t>2026-10-31 14:48:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-30 21:32:24</t>
+          <t>2026-10-31 14:48:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-30 21:32:24</t>
+          <t>2026-10-31 14:48:54</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-30 21:32:24</t>
+          <t>2026-10-31 14:48:54</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-30 21:32:24</t>
+          <t>2026-10-31 14:48:54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-30 21:32:24</t>
+          <t>2026-10-31 14:48:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06 15:22:40</t>
+          <t>2026-10-06 21:36:25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,12 +1655,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C15">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-28 21:31:01</t>
+          <t>2026-10-29 14:51:22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-29 14:51:22</t>
+          <t>2026-10-29 21:42:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-29 21:42:30</t>
+          <t>2026-10-30 14:54:51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-30 14:54:51</t>
+          <t>2026-10-30 21:32:24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-30 21:32:24</t>
+          <t>2026-10-31 14:48:54</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">

--- a/reports/holding_plan.xlsx
+++ b/reports/holding_plan.xlsx
@@ -98,7 +98,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-31 14:48:54</t>
+          <t>2026-10-31 21:03:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -311,7 +311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-31 14:48:54</t>
+          <t>2026-10-31 21:03:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -398,7 +398,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-31 14:48:54</t>
+          <t>2026-10-31 21:03:01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-31 14:48:54</t>
+          <t>2026-10-31 21:03:01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-31 14:48:54</t>
+          <t>2026-10-31 21:03:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-31 14:48:54</t>
+          <t>2026-10-31 21:03:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06 21:36:25</t>
+          <t>2026-10-07 15:01:26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1343,7 +1343,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07 15:01:26</t>
+          <t>2026-10-07 21:54:22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07 21:54:22</t>
+          <t>2026-10-08 15:09:53</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08 15:09:53</t>
+          <t>2026-10-08 22:00:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08 22:00:49</t>
+          <t>2026-10-09 15:14:37</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09 15:14:37</t>
+          <t>2026-10-09 21:44:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1473,7 +1473,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09 21:44:45</t>
+          <t>2026-10-10 14:51:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-10 14:51:17</t>
+          <t>2026-10-10 21:02:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-10 21:02:32</t>
+          <t>2026-10-11 14:56:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-11 14:56:25</t>
+          <t>2026-10-11 21:30:39</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1577,7 +1577,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-11 21:30:39</t>
+          <t>2026-10-12 15:07:46</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1603,12 +1603,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-12 15:07:46</t>
+          <t>2026-10-13 00:05:14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13">
@@ -1629,12 +1629,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-13 00:05:14</t>
+          <t>2026-10-13 15:32:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="C14">
@@ -1655,7 +1655,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-13 15:32:12</t>
+          <t>2026-10-13 22:33:48</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-13 22:33:48</t>
+          <t>2026-10-14 13:56:50</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-14 13:56:50</t>
+          <t>2026-10-14 20:21:38</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-14 20:21:38</t>
+          <t>2026-10-15 13:43:04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15 13:43:04</t>
+          <t>2026-10-15 20:06:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15 20:06:27</t>
+          <t>2026-10-16 13:38:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16 13:38:22</t>
+          <t>2026-10-16 19:53:40</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16 19:53:40</t>
+          <t>2026-10-17 13:24:52</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17 13:24:52</t>
+          <t>2026-10-17 19:09:48</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17 19:09:48</t>
+          <t>2026-10-18 13:35:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-18 13:35:44</t>
+          <t>2026-10-18 19:41:16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-18 19:41:16</t>
+          <t>2026-10-19 13:53:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1967,7 +1967,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-19 13:53:52</t>
+          <t>2026-10-19 21:55:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-19 21:55:57</t>
+          <t>2026-10-20 13:46:12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-20 13:46:12</t>
+          <t>2026-10-20 20:09:27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-20 20:09:27</t>
+          <t>2026-10-21 13:50:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-21 13:50:07</t>
+          <t>2026-10-21 20:23:23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2097,7 +2097,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-21 20:23:23</t>
+          <t>2026-10-22 13:52:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-22 13:52:59</t>
+          <t>2026-10-22 20:23:43</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2149,7 +2149,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-22 20:23:43</t>
+          <t>2026-10-23 13:51:16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-23 13:51:16</t>
+          <t>2026-10-23 20:05:29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-23 20:05:29</t>
+          <t>2026-10-24 13:34:19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-24 13:34:19</t>
+          <t>2026-10-24 19:37:14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-24 19:37:14</t>
+          <t>2026-10-25 13:49:54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-25 13:49:54</t>
+          <t>2026-10-25 19:58:43</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2305,7 +2305,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-25 19:58:43</t>
+          <t>2026-10-26 13:52:53</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-26 13:52:53</t>
+          <t>2026-10-26 21:32:44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-26 21:32:44</t>
+          <t>2026-10-27 14:05:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2383,7 +2383,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-27 14:05:47</t>
+          <t>2026-10-27 20:39:30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-27 20:39:30</t>
+          <t>2026-10-28 14:43:47</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-28 14:43:47</t>
+          <t>2026-10-28 21:31:01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-28 21:31:01</t>
+          <t>2026-10-29 14:51:22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-29 14:51:22</t>
+          <t>2026-10-29 21:42:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2513,7 +2513,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-29 21:42:30</t>
+          <t>2026-10-30 14:54:51</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-30 14:54:51</t>
+          <t>2026-10-30 21:32:24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-30 21:32:24</t>
+          <t>2026-10-31 14:48:54</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2591,7 +2591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-31 14:48:54</t>
+          <t>2026-10-31 21:03:01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
